--- a/pensum/ol14/OL14_Klasseoppgaver_v5.xlsx
+++ b/pensum/ol14/OL14_Klasseoppgaver_v5.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="152">
   <si>
     <t xml:space="preserve">Klasseoppgaver til Organisasjon og ledelse kapittel 14: Klassiske organisasjonsteorier (V5)</t>
   </si>
@@ -161,18 +161,48 @@
     <t xml:space="preserve">a)  Hva taper Nordlys i året hvis normtiden er satt én time for lavt? Antall skap ganger én time ganger timeprisen.</t>
   </si>
   <si>
+    <t xml:space="preserve">Formel og begrep</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tap i året = antall jobber × timer feil × timepris. Tidsstudien fastsetter normtallet for en oppgave (Organisasjon og ledelse 14.1).</t>
+  </si>
+  <si>
     <t xml:space="preserve">b)  Akkordlagene bruker 11 timer i stedet for 14. Hva er de frigjorte timene verdt i året, hvis de selges til andre kunder?</t>
   </si>
   <si>
+    <t xml:space="preserve">Frigjort verdi = (normtid − faktisk tid) × antall jobber × timepris. Metodestudier og akkord skal gi lavest mulig forbruk av tid (Organisasjon og ledelse 14.1).</t>
+  </si>
+  <si>
     <t xml:space="preserve">c)  Hva er det umålte arbeidet (en halv time per skap) verdt i året, regnet med timeprisen?</t>
   </si>
   <si>
+    <t xml:space="preserve">Verdi = timer × antall jobber × timepris. Det som ikke har et normtall fra tidsstudien, blir ikke målt (Organisasjon og ledelse 14.1).</t>
+  </si>
+  <si>
     <t xml:space="preserve">d)  Akkordlaget gjorde alle skapene på 11 timer i mars, men det kom ingen nye oppdrag å sette dem på. Hva tjente Nordlys på de sparte timene?   A: 2 670 kr per skap (3 timer × 890 kr)   B: Ingenting ennå: gevinsten blir ekte først når timene selges til en annen kunde   C: Mer enn 2 670 kr per skap, fordi montørene tjente mer   (skriv bokstaven)</t>
   </si>
   <si>
     <t xml:space="preserve">e)  Et styremedlem vil innføre akkord også i service, «siden det virker i prosjekt». Hva svarer du? Bruk Taylor og minst ett tall. To–tre setninger.</t>
   </si>
   <si>
+    <t xml:space="preserve">Vitenskapelig ledelse: metodestudier, tidsstudier og prestasjonslønn (Organisasjon og ledelse 14.1). Gruppenormer og akkord i Hawthorne-undersøkelsene (15.1).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hint, hvis du står fast</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fra timer til kroner</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gang antall skap med timene og timeprisen. Én time for lav: 120 × 1 × 890. Akkorden frigjør 14 − 11 = 3 timer per skap. Det umålte er en halv time per skap.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Når er gevinsten ekte?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">En spart time er verdt 890 kr bare når den selges til en annen kunde. Står laget uten oppdrag, er den spart på papiret og ingen andre steder.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Kilde: Hjertnes, F.: Markedsføring, organisasjon og ledelse for LØM-emnet, kap. 14.1 (vitenskapelig ledelse: metodestudier, tidsstudier, prestasjonslønn og akkordlønn) og kap. 15.1 (gruppenormer og akkord i Hawthorne-undersøkelsene). Tallene er de samme som i appen og øvingsheftet til kap. 14. Nordlys Elektro AS er en konstruert casebedrift.</t>
   </si>
   <si>
@@ -245,12 +275,30 @@
     <t xml:space="preserve">c)  Hvor stor andel av montørenes betalte timer blir fakturert? Fakturerbare timer delt på alle betalte timer for de to montørene, i prosent med én desimal.</t>
   </si>
   <si>
+    <t xml:space="preserve">Faktureringsgrad = fakturerbare timer / betalte timer × 100. Et mål på indre effektivitet: å løse oppgavene med lavest mulig ressursforbruk (effektivitetsavsnittet etter 14.3).</t>
+  </si>
+  <si>
     <t xml:space="preserve">d)  Mona sier: «77,8 % av timene blir fakturert. Da er vi en effektiv bedrift.» Hva sier læreboka?   A: Riktig: høy faktureringsgrad betyr at bedriften er effektiv   B: Tallet måler indre effektivitet. Bedriften er først effektiv når den også gjør det markedet vil ha (ytre effektivitet)   C: Tallet måler ytre effektivitet, fordi kundene betaler for timene   (skriv bokstaven)</t>
   </si>
   <si>
     <t xml:space="preserve">e)  Hva svarer Mona montøren som kaller internkontrollen «bare byråkrati»? Bruk Weber, og nevn én ulempe ved regelstyring. To–tre setninger.</t>
   </si>
   <si>
+    <t xml:space="preserve">Byråkratiteorien (Organisasjon og ledelse 14.3) og regelstyring: forutsigbarhet og effektiv produksjon, men mindre kreativitet og skjønn (17.9.2). Dokumentasjonskravene står ikke i boka: forskrift om elektriske lavspenningsanlegg (FEL) § 12 og internkontrollforskriften § 5.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hvem står bak?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weber: autoritet i stillingen, formell kompetanse, habilitet. Taylor: normtid og tidsstudier. Lagets egne normer er Hawthorne (kap. 15), ikke Weber.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Faktureringsgraden</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fakturerbare timer delt på betalte timer for montørene: 2 × 1 400 delt på 2 × 1 800. Tallet sier hvor godt Fjell gjør tingene riktig, ikke om det er de riktige tingene.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Kilde: Hjertnes, F.: Markedsføring, organisasjon og ledelse for LØM-emnet, kap. 14.2 (enhetlig ledelse), 14.3 (byråkratiteorien) og avsnittet om indre og ytre effektivitet. FEL § 12 og internkontrollforskriften § 5 (Lovdata). Fjell Elektro AS er en konstruert casebedrift.</t>
   </si>
   <si>
@@ -314,9 +362,15 @@
     <t xml:space="preserve">a)  Hva er Karis kontrollspenn i dag, altså antall personer hun har direkte under seg?</t>
   </si>
   <si>
+    <t xml:space="preserve">Kontrollspenn = antall direkte underordnede. Kontrollspennet må være begrenset; seks til ti anses optimalt (Fayol, Organisasjon og ledelse 14.2).</t>
+  </si>
+  <si>
     <t xml:space="preserve">b)  Hva blir Ronnys kontrollspenn hvis de to solcellemontørene legges under ham?</t>
   </si>
   <si>
+    <t xml:space="preserve">Kontrollspenn: seks til ti underordnede anses optimalt (Fayol, Organisasjon og ledelse 14.2).</t>
+  </si>
+  <si>
     <t xml:space="preserve">c)  Nordlys er delt i service, prosjekt og nybygg, og solcelle og lading. Hvilken variant av linjeorganisasjonen er det?   A: Funksjonsdelt   B: Produktdelt   C: Markedsdelt   (skriv bokstaven)</t>
   </si>
   <si>
@@ -326,6 +380,21 @@
     <t xml:space="preserve">e)  Anbefal Kari ett nytt kart for solcelle og lading. Si hvilket av Fayols prinsipper du retter, hva det koster, og hva som blir verre. Minst ett tall.</t>
   </si>
   <si>
+    <t xml:space="preserve">Enhetlig ledelse, kontrollspenn og få nivåer (Fayol, Organisasjon og ledelse 14.2), stab og linje (14.4).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tell riktig</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kontrollspenn er de direkte underordnede, ikke alle i avdelingen. Kari: Tom, Ronny, Ida og de to solcellemontørene. Ronny har 7 i dag; legg til de to.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linje og stab</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Staben står under toppledelsen og utenfor linjen. Den gir råd og har ikke ordregivende myndighet (14.4). Variantene skiller seg i hva avdelingene deles etter.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Kilde: Hjertnes, F.: Markedsføring, organisasjon og ledelse for LØM-emnet, kap. 14.2 (enhetlig ledelse, kontrollspenn 6–10), 14.4 (linjeorganisasjon og stab) og 14.6 (produktdelt linjeorganisasjon). Kartet er det samme som i appen og øvingsheftet til kap. 14. Nordlys Elektro AS er en konstruert casebedrift.</t>
   </si>
   <si>
@@ -377,9 +446,15 @@
     <t xml:space="preserve">a)  Hva er Monas kontrollspenn i modell 1, der alle rapporterer direkte til henne?</t>
   </si>
   <si>
+    <t xml:space="preserve">Kontrollspenn = antall direkte underordnede; seks til ti anses optimalt (Fayol, Organisasjon og ledelse 14.2).</t>
+  </si>
+  <si>
     <t xml:space="preserve">b)  Hva er Monas kontrollspenn i modell 2, med to formenn?</t>
   </si>
   <si>
+    <t xml:space="preserve">Kontrollspenn og antall nivåer: kontrollspennet må være begrenset, og antall nivåer mellom topp og bunn bør være så lavt som mulig (Fayol, Organisasjon og ledelse 14.2).</t>
+  </si>
+  <si>
     <t xml:space="preserve">c)  I modell 2 deles lagene etter kundene: boligkunder, og bedrifter og borettslag. Hvilken variant av linjeorganisasjonen er det?   A: Funksjonsdelt   B: Produktdelt   C: Markedsdelt   (skriv bokstaven)</t>
   </si>
   <si>
@@ -387,6 +462,21 @@
   </si>
   <si>
     <t xml:space="preserve">e)  Hvilken modell anbefaler du Mona, og hva koster den? Bruk kontrollspenn og minst én fordel og én ulempe. To–tre setninger.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kontrollspenn og nivåer (Fayol, 14.2), markedsdelt linjeorganisasjon (14.7), suboptimalisering (14.4–14.5) og valg av organisasjonsmodell (Organisasjon og ledelse, avsnittet etter 14.7).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tell og plasser</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Modell 1: alle 8 under Mona. Modell 2: bare formennene står direkte under henne. Lag delt etter kundetype er én av de tre variantene i 14.5–14.7.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bonus per lag</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spør: hva gjør et lag som bare måles på egne timer når det andre laget trenger en montør i to dager? Boka kaller det suboptimalisering.</t>
   </si>
   <si>
     <t xml:space="preserve">Kilde: Hjertnes, F.: Markedsføring, organisasjon og ledelse for LØM-emnet, kap. 14.2 (kontrollspenn, nivåer), 14.4 (linjeorganisasjon, suboptimalisering), 14.5–14.7 (de tre variantene) og avsnittet om valg av organisasjonsmodell. Fjell Elektro AS er en konstruert casebedrift.</t>
@@ -400,7 +490,7 @@
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="#,##0.##;\−#,##0.##;\0"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="13">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -467,8 +557,30 @@
       <family val="0"/>
       <charset val="1"/>
     </font>
+    <font>
+      <b val="true"/>
+      <sz val="10"/>
+      <color rgb="FF2F4A6D"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="10"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -484,13 +596,31 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFF4F6FA"/>
-        <bgColor rgb="FFFFFFFF"/>
+        <bgColor rgb="FFEEF2F8"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
         <bgColor rgb="FFFFFF00"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEEF2F8"/>
+        <bgColor rgb="FFF4F6FA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB8954A"/>
+        <bgColor rgb="FF808080"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBF6EA"/>
+        <bgColor rgb="FFF4F6FA"/>
       </patternFill>
     </fill>
   </fills>
@@ -543,7 +673,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="25">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -612,11 +742,31 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="10" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -653,8 +803,8 @@
       <rgbColor rgb="FF808080"/>
       <rgbColor rgb="FF9999FF"/>
       <rgbColor rgb="FF993366"/>
-      <rgbColor rgb="FFF4F6FA"/>
-      <rgbColor rgb="FFCCFFFF"/>
+      <rgbColor rgb="FFFBF6EA"/>
+      <rgbColor rgb="FFEEF2F8"/>
       <rgbColor rgb="FF660066"/>
       <rgbColor rgb="FFFF8080"/>
       <rgbColor rgb="FF0066CC"/>
@@ -668,7 +818,7 @@
       <rgbColor rgb="FF008080"/>
       <rgbColor rgb="FF0000FF"/>
       <rgbColor rgb="FF00CCFF"/>
-      <rgbColor rgb="FFCCFFFF"/>
+      <rgbColor rgb="FFF4F6FA"/>
       <rgbColor rgb="FFCCFFCC"/>
       <rgbColor rgb="FFFFFF99"/>
       <rgbColor rgb="FF99CCFF"/>
@@ -682,7 +832,7 @@
       <rgbColor rgb="FFFF9900"/>
       <rgbColor rgb="FFFF6600"/>
       <rgbColor rgb="FF5E6670"/>
-      <rgbColor rgb="FF969696"/>
+      <rgbColor rgb="FFB8954A"/>
       <rgbColor rgb="FF003366"/>
       <rgbColor rgb="FF339966"/>
       <rgbColor rgb="FF003300"/>
@@ -985,7 +1135,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:G28"/>
+  <dimension ref="A1:G40"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="34"/>
@@ -1130,35 +1280,20 @@
         <v/>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="7" t="s">
+    <row r="19" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="17" t="s">
         <v>45</v>
       </c>
-      <c r="B19" s="7"/>
-      <c r="C19" s="7"/>
-      <c r="D19" s="7"/>
-      <c r="E19" s="7"/>
-      <c r="F19" s="15"/>
-      <c r="G19" s="16" t="str">
-        <f aca="false">IF(F19="","",IF(ABS(F19-(320400))&lt;=0.000000001,"Riktig","Prøv igjen"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="7" t="s">
+      <c r="B19" s="18" t="s">
         <v>46</v>
       </c>
-      <c r="B20" s="7"/>
-      <c r="C20" s="7"/>
-      <c r="D20" s="7"/>
-      <c r="E20" s="7"/>
-      <c r="F20" s="15"/>
-      <c r="G20" s="16" t="str">
-        <f aca="false">IF(F20="","",IF(ABS(F20-(53400))&lt;=0.000000001,"Riktig","Prøv igjen"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C19" s="18"/>
+      <c r="D19" s="18"/>
+      <c r="E19" s="18"/>
+      <c r="F19" s="18"/>
+      <c r="G19" s="18"/>
+    </row>
+    <row r="21" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="7" t="s">
         <v>47</v>
       </c>
@@ -1166,42 +1301,46 @@
       <c r="C21" s="7"/>
       <c r="D21" s="7"/>
       <c r="E21" s="7"/>
-      <c r="F21" s="17"/>
+      <c r="F21" s="15"/>
       <c r="G21" s="16" t="str">
-        <f aca="false">IF(F21="","",IF(UPPER(TRIM(F21))="B","Riktig","Prøv igjen"))</f>
+        <f aca="false">IF(F21="","",IF(ABS(F21-(320400))&lt;=0.000000001,"Riktig","Prøv igjen"))</f>
         <v/>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="7" t="s">
+    <row r="22" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="17" t="s">
+        <v>45</v>
+      </c>
+      <c r="B22" s="18" t="s">
         <v>48</v>
       </c>
-      <c r="B22" s="7"/>
-      <c r="C22" s="7"/>
-      <c r="D22" s="7"/>
-      <c r="E22" s="7"/>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="18"/>
-      <c r="B23" s="18"/>
-      <c r="C23" s="18"/>
-      <c r="D23" s="18"/>
-      <c r="E23" s="18"/>
-      <c r="F23" s="18"/>
-      <c r="G23" s="18"/>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="18"/>
-      <c r="B24" s="18"/>
-      <c r="C24" s="18"/>
-      <c r="D24" s="18"/>
-      <c r="E24" s="18"/>
-      <c r="F24" s="18"/>
-      <c r="G24" s="18"/>
-    </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="18"/>
-      <c r="B25" s="18"/>
+      <c r="C22" s="18"/>
+      <c r="D22" s="18"/>
+      <c r="E22" s="18"/>
+      <c r="F22" s="18"/>
+      <c r="G22" s="18"/>
+    </row>
+    <row r="24" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="B24" s="7"/>
+      <c r="C24" s="7"/>
+      <c r="D24" s="7"/>
+      <c r="E24" s="7"/>
+      <c r="F24" s="15"/>
+      <c r="G24" s="16" t="str">
+        <f aca="false">IF(F24="","",IF(ABS(F24-(53400))&lt;=0.000000001,"Riktig","Prøv igjen"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="17" t="s">
+        <v>45</v>
+      </c>
+      <c r="B25" s="18" t="s">
+        <v>50</v>
+      </c>
       <c r="C25" s="18"/>
       <c r="D25" s="18"/>
       <c r="E25" s="18"/>
@@ -1209,41 +1348,148 @@
       <c r="G25" s="18"/>
     </row>
     <row r="27" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="B27" s="6"/>
-      <c r="C27" s="6"/>
-      <c r="D27" s="6"/>
-      <c r="E27" s="6"/>
-      <c r="F27" s="6"/>
-      <c r="G27" s="6"/>
-    </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="B28" s="6"/>
-      <c r="C28" s="6"/>
-      <c r="D28" s="6"/>
-      <c r="E28" s="6"/>
-      <c r="F28" s="6"/>
-      <c r="G28" s="6"/>
+      <c r="A27" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="B27" s="7"/>
+      <c r="C27" s="7"/>
+      <c r="D27" s="7"/>
+      <c r="E27" s="7"/>
+      <c r="F27" s="19"/>
+      <c r="G27" s="16" t="str">
+        <f aca="false">IF(F27="","",IF(UPPER(TRIM(F27))="B","Riktig","Prøv igjen"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="B28" s="7"/>
+      <c r="C28" s="7"/>
+      <c r="D28" s="7"/>
+      <c r="E28" s="7"/>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="20"/>
+      <c r="B29" s="20"/>
+      <c r="C29" s="20"/>
+      <c r="D29" s="20"/>
+      <c r="E29" s="20"/>
+      <c r="F29" s="20"/>
+      <c r="G29" s="20"/>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="20"/>
+      <c r="B30" s="20"/>
+      <c r="C30" s="20"/>
+      <c r="D30" s="20"/>
+      <c r="E30" s="20"/>
+      <c r="F30" s="20"/>
+      <c r="G30" s="20"/>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="20"/>
+      <c r="B31" s="20"/>
+      <c r="C31" s="20"/>
+      <c r="D31" s="20"/>
+      <c r="E31" s="20"/>
+      <c r="F31" s="20"/>
+      <c r="G31" s="20"/>
+    </row>
+    <row r="32" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="17" t="s">
+        <v>45</v>
+      </c>
+      <c r="B32" s="18" t="s">
+        <v>53</v>
+      </c>
+      <c r="C32" s="18"/>
+      <c r="D32" s="18"/>
+      <c r="E32" s="18"/>
+      <c r="F32" s="18"/>
+      <c r="G32" s="18"/>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="21" t="s">
+        <v>54</v>
+      </c>
+      <c r="B35" s="21"/>
+      <c r="C35" s="21"/>
+      <c r="D35" s="21"/>
+      <c r="E35" s="21"/>
+      <c r="F35" s="21"/>
+      <c r="G35" s="21"/>
+    </row>
+    <row r="36" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="22" t="s">
+        <v>55</v>
+      </c>
+      <c r="B36" s="23" t="s">
+        <v>56</v>
+      </c>
+      <c r="C36" s="23"/>
+      <c r="D36" s="23"/>
+      <c r="E36" s="23"/>
+      <c r="F36" s="23"/>
+      <c r="G36" s="23"/>
+    </row>
+    <row r="37" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A37" s="22" t="s">
+        <v>57</v>
+      </c>
+      <c r="B37" s="23" t="s">
+        <v>58</v>
+      </c>
+      <c r="C37" s="23"/>
+      <c r="D37" s="23"/>
+      <c r="E37" s="23"/>
+      <c r="F37" s="23"/>
+      <c r="G37" s="23"/>
+    </row>
+    <row r="39" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A39" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="B39" s="6"/>
+      <c r="C39" s="6"/>
+      <c r="D39" s="6"/>
+      <c r="E39" s="6"/>
+      <c r="F39" s="6"/>
+      <c r="G39" s="6"/>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A40" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="B40" s="6"/>
+      <c r="C40" s="6"/>
+      <c r="D40" s="6"/>
+      <c r="E40" s="6"/>
+      <c r="F40" s="6"/>
+      <c r="G40" s="6"/>
     </row>
   </sheetData>
-  <mergeCells count="12">
+  <mergeCells count="19">
     <mergeCell ref="A4:G4"/>
     <mergeCell ref="A5:G5"/>
     <mergeCell ref="A15:G15"/>
     <mergeCell ref="A17:E17"/>
     <mergeCell ref="A18:E18"/>
-    <mergeCell ref="A19:E19"/>
-    <mergeCell ref="A20:E20"/>
+    <mergeCell ref="B19:G19"/>
     <mergeCell ref="A21:E21"/>
-    <mergeCell ref="A22:E22"/>
-    <mergeCell ref="A23:G25"/>
-    <mergeCell ref="A27:G27"/>
-    <mergeCell ref="A28:G28"/>
+    <mergeCell ref="B22:G22"/>
+    <mergeCell ref="A24:E24"/>
+    <mergeCell ref="B25:G25"/>
+    <mergeCell ref="A27:E27"/>
+    <mergeCell ref="A28:E28"/>
+    <mergeCell ref="A29:G31"/>
+    <mergeCell ref="B32:G32"/>
+    <mergeCell ref="A35:G35"/>
+    <mergeCell ref="B36:G36"/>
+    <mergeCell ref="B37:G37"/>
+    <mergeCell ref="A39:G39"/>
+    <mergeCell ref="A40:G40"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -1260,7 +1506,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:G31"/>
+  <dimension ref="A1:G39"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="34"/>
@@ -1271,7 +1517,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1281,7 +1527,7 @@
     </row>
     <row r="4" customFormat="false" ht="78.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="B4" s="6"/>
       <c r="C4" s="6"/>
@@ -1292,7 +1538,7 @@
     </row>
     <row r="5" customFormat="false" ht="108.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="7" t="s">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="B5" s="7"/>
       <c r="C5" s="7"/>
@@ -1315,11 +1561,11 @@
       <c r="G7" s="14"/>
     </row>
     <row r="8" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="19" t="s">
-        <v>54</v>
+      <c r="A8" s="24" t="s">
+        <v>64</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="C8" s="7"/>
       <c r="D8" s="7"/>
@@ -1328,11 +1574,11 @@
       <c r="G8" s="7"/>
     </row>
     <row r="9" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="19" t="s">
-        <v>56</v>
+      <c r="A9" s="24" t="s">
+        <v>66</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="C9" s="7"/>
       <c r="D9" s="7"/>
@@ -1341,11 +1587,11 @@
       <c r="G9" s="7"/>
     </row>
     <row r="10" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="19" t="s">
-        <v>58</v>
+      <c r="A10" s="24" t="s">
+        <v>68</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="C10" s="7"/>
       <c r="D10" s="7"/>
@@ -1354,11 +1600,11 @@
       <c r="G10" s="7"/>
     </row>
     <row r="11" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="19" t="s">
-        <v>60</v>
+      <c r="A11" s="24" t="s">
+        <v>70</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="C11" s="7"/>
       <c r="D11" s="7"/>
@@ -1367,11 +1613,11 @@
       <c r="G11" s="7"/>
     </row>
     <row r="12" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="19" t="s">
-        <v>62</v>
+      <c r="A12" s="24" t="s">
+        <v>72</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="C12" s="7"/>
       <c r="D12" s="7"/>
@@ -1396,7 +1642,7 @@
     </row>
     <row r="15" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="7" t="s">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="B15" s="7"/>
       <c r="C15" s="7"/>
@@ -1405,13 +1651,13 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="7" t="s">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="B16" s="7"/>
       <c r="C16" s="7"/>
       <c r="D16" s="7"/>
       <c r="E16" s="7"/>
-      <c r="F16" s="17"/>
+      <c r="F16" s="19"/>
       <c r="G16" s="16" t="str">
         <f aca="false">IF(F16="","",IF(UPPER(TRIM(F16))="JA","Riktig","Prøv igjen"))</f>
         <v/>
@@ -1419,13 +1665,13 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="7" t="s">
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="B17" s="7"/>
       <c r="C17" s="7"/>
       <c r="D17" s="7"/>
       <c r="E17" s="7"/>
-      <c r="F17" s="17"/>
+      <c r="F17" s="19"/>
       <c r="G17" s="16" t="str">
         <f aca="false">IF(F17="","",IF(UPPER(TRIM(F17))="JA","Riktig","Prøv igjen"))</f>
         <v/>
@@ -1433,13 +1679,13 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="7" t="s">
-        <v>67</v>
+        <v>77</v>
       </c>
       <c r="B18" s="7"/>
       <c r="C18" s="7"/>
       <c r="D18" s="7"/>
       <c r="E18" s="7"/>
-      <c r="F18" s="17"/>
+      <c r="F18" s="19"/>
       <c r="G18" s="16" t="str">
         <f aca="false">IF(F18="","",IF(UPPER(TRIM(F18))="JA","Riktig","Prøv igjen"))</f>
         <v/>
@@ -1447,13 +1693,13 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="7" t="s">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="B19" s="7"/>
       <c r="C19" s="7"/>
       <c r="D19" s="7"/>
       <c r="E19" s="7"/>
-      <c r="F19" s="17"/>
+      <c r="F19" s="19"/>
       <c r="G19" s="16" t="str">
         <f aca="false">IF(F19="","",IF(UPPER(TRIM(F19))="NEI","Riktig","Prøv igjen"))</f>
         <v/>
@@ -1461,13 +1707,13 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="7" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="B20" s="7"/>
       <c r="C20" s="7"/>
       <c r="D20" s="7"/>
       <c r="E20" s="7"/>
-      <c r="F20" s="17"/>
+      <c r="F20" s="19"/>
       <c r="G20" s="16" t="str">
         <f aca="false">IF(F20="","",IF(UPPER(TRIM(F20))="NEI","Riktig","Prøv igjen"))</f>
         <v/>
@@ -1475,13 +1721,13 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="7" t="s">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="B21" s="7"/>
       <c r="C21" s="7"/>
       <c r="D21" s="7"/>
       <c r="E21" s="7"/>
-      <c r="F21" s="17"/>
+      <c r="F21" s="19"/>
       <c r="G21" s="16" t="str">
         <f aca="false">IF(F21="","",IF(UPPER(TRIM(F21))="NEI","Riktig","Prøv igjen"))</f>
         <v/>
@@ -1489,13 +1735,13 @@
     </row>
     <row r="22" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="7" t="s">
-        <v>71</v>
+        <v>81</v>
       </c>
       <c r="B22" s="7"/>
       <c r="C22" s="7"/>
       <c r="D22" s="7"/>
       <c r="E22" s="7"/>
-      <c r="F22" s="17"/>
+      <c r="F22" s="19"/>
       <c r="G22" s="16" t="str">
         <f aca="false">IF(F22="","",IF(UPPER(TRIM(F22))="B","Riktig","Prøv igjen"))</f>
         <v/>
@@ -1503,7 +1749,7 @@
     </row>
     <row r="23" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="7" t="s">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="B23" s="7"/>
       <c r="C23" s="7"/>
@@ -1515,80 +1761,143 @@
         <v/>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="B24" s="7"/>
-      <c r="C24" s="7"/>
-      <c r="D24" s="7"/>
-      <c r="E24" s="7"/>
-      <c r="F24" s="17"/>
-      <c r="G24" s="16" t="str">
-        <f aca="false">IF(F24="","",IF(UPPER(TRIM(F24))="B","Riktig","Prøv igjen"))</f>
+    <row r="24" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="17" t="s">
+        <v>45</v>
+      </c>
+      <c r="B24" s="18" t="s">
+        <v>83</v>
+      </c>
+      <c r="C24" s="18"/>
+      <c r="D24" s="18"/>
+      <c r="E24" s="18"/>
+      <c r="F24" s="18"/>
+      <c r="G24" s="18"/>
+    </row>
+    <row r="26" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="B26" s="7"/>
+      <c r="C26" s="7"/>
+      <c r="D26" s="7"/>
+      <c r="E26" s="7"/>
+      <c r="F26" s="19"/>
+      <c r="G26" s="16" t="str">
+        <f aca="false">IF(F26="","",IF(UPPER(TRIM(F26))="B","Riktig","Prøv igjen"))</f>
         <v/>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="7" t="s">
-        <v>74</v>
-      </c>
-      <c r="B25" s="7"/>
-      <c r="C25" s="7"/>
-      <c r="D25" s="7"/>
-      <c r="E25" s="7"/>
-    </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="18"/>
-      <c r="B26" s="18"/>
-      <c r="C26" s="18"/>
-      <c r="D26" s="18"/>
-      <c r="E26" s="18"/>
-      <c r="F26" s="18"/>
-      <c r="G26" s="18"/>
-    </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="18"/>
-      <c r="B27" s="18"/>
-      <c r="C27" s="18"/>
-      <c r="D27" s="18"/>
-      <c r="E27" s="18"/>
-      <c r="F27" s="18"/>
-      <c r="G27" s="18"/>
+    <row r="27" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="B27" s="7"/>
+      <c r="C27" s="7"/>
+      <c r="D27" s="7"/>
+      <c r="E27" s="7"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="18"/>
-      <c r="B28" s="18"/>
-      <c r="C28" s="18"/>
-      <c r="D28" s="18"/>
-      <c r="E28" s="18"/>
-      <c r="F28" s="18"/>
-      <c r="G28" s="18"/>
-    </row>
-    <row r="30" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="6" t="s">
-        <v>75</v>
-      </c>
-      <c r="B30" s="6"/>
-      <c r="C30" s="6"/>
-      <c r="D30" s="6"/>
-      <c r="E30" s="6"/>
-      <c r="F30" s="6"/>
-      <c r="G30" s="6"/>
-    </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="B31" s="6"/>
-      <c r="C31" s="6"/>
-      <c r="D31" s="6"/>
-      <c r="E31" s="6"/>
-      <c r="F31" s="6"/>
-      <c r="G31" s="6"/>
+      <c r="A28" s="20"/>
+      <c r="B28" s="20"/>
+      <c r="C28" s="20"/>
+      <c r="D28" s="20"/>
+      <c r="E28" s="20"/>
+      <c r="F28" s="20"/>
+      <c r="G28" s="20"/>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="20"/>
+      <c r="B29" s="20"/>
+      <c r="C29" s="20"/>
+      <c r="D29" s="20"/>
+      <c r="E29" s="20"/>
+      <c r="F29" s="20"/>
+      <c r="G29" s="20"/>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="20"/>
+      <c r="B30" s="20"/>
+      <c r="C30" s="20"/>
+      <c r="D30" s="20"/>
+      <c r="E30" s="20"/>
+      <c r="F30" s="20"/>
+      <c r="G30" s="20"/>
+    </row>
+    <row r="31" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="17" t="s">
+        <v>45</v>
+      </c>
+      <c r="B31" s="18" t="s">
+        <v>86</v>
+      </c>
+      <c r="C31" s="18"/>
+      <c r="D31" s="18"/>
+      <c r="E31" s="18"/>
+      <c r="F31" s="18"/>
+      <c r="G31" s="18"/>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="21" t="s">
+        <v>54</v>
+      </c>
+      <c r="B34" s="21"/>
+      <c r="C34" s="21"/>
+      <c r="D34" s="21"/>
+      <c r="E34" s="21"/>
+      <c r="F34" s="21"/>
+      <c r="G34" s="21"/>
+    </row>
+    <row r="35" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A35" s="22" t="s">
+        <v>87</v>
+      </c>
+      <c r="B35" s="23" t="s">
+        <v>88</v>
+      </c>
+      <c r="C35" s="23"/>
+      <c r="D35" s="23"/>
+      <c r="E35" s="23"/>
+      <c r="F35" s="23"/>
+      <c r="G35" s="23"/>
+    </row>
+    <row r="36" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="22" t="s">
+        <v>89</v>
+      </c>
+      <c r="B36" s="23" t="s">
+        <v>90</v>
+      </c>
+      <c r="C36" s="23"/>
+      <c r="D36" s="23"/>
+      <c r="E36" s="23"/>
+      <c r="F36" s="23"/>
+      <c r="G36" s="23"/>
+    </row>
+    <row r="38" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A38" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="B38" s="6"/>
+      <c r="C38" s="6"/>
+      <c r="D38" s="6"/>
+      <c r="E38" s="6"/>
+      <c r="F38" s="6"/>
+      <c r="G38" s="6"/>
+    </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A39" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="B39" s="6"/>
+      <c r="C39" s="6"/>
+      <c r="D39" s="6"/>
+      <c r="E39" s="6"/>
+      <c r="F39" s="6"/>
+      <c r="G39" s="6"/>
     </row>
   </sheetData>
-  <mergeCells count="23">
+  <mergeCells count="28">
     <mergeCell ref="A4:G4"/>
     <mergeCell ref="A5:G5"/>
     <mergeCell ref="B7:G7"/>
@@ -1607,11 +1916,16 @@
     <mergeCell ref="A21:E21"/>
     <mergeCell ref="A22:E22"/>
     <mergeCell ref="A23:E23"/>
-    <mergeCell ref="A24:E24"/>
-    <mergeCell ref="A25:E25"/>
-    <mergeCell ref="A26:G28"/>
-    <mergeCell ref="A30:G30"/>
-    <mergeCell ref="A31:G31"/>
+    <mergeCell ref="B24:G24"/>
+    <mergeCell ref="A26:E26"/>
+    <mergeCell ref="A27:E27"/>
+    <mergeCell ref="A28:G30"/>
+    <mergeCell ref="B31:G31"/>
+    <mergeCell ref="A34:G34"/>
+    <mergeCell ref="B35:G35"/>
+    <mergeCell ref="B36:G36"/>
+    <mergeCell ref="A38:G38"/>
+    <mergeCell ref="A39:G39"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -1628,7 +1942,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:G28"/>
+  <dimension ref="A1:G38"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="34"/>
@@ -1639,7 +1953,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>76</v>
+        <v>92</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1649,7 +1963,7 @@
     </row>
     <row r="4" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>77</v>
+        <v>93</v>
       </c>
       <c r="B4" s="6"/>
       <c r="C4" s="6"/>
@@ -1660,7 +1974,7 @@
     </row>
     <row r="5" customFormat="false" ht="108.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="7" t="s">
-        <v>78</v>
+        <v>94</v>
       </c>
       <c r="B5" s="7"/>
       <c r="C5" s="7"/>
@@ -1671,66 +1985,66 @@
     </row>
     <row r="7" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="8" t="s">
-        <v>79</v>
+        <v>95</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>80</v>
+        <v>96</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="10" t="s">
-        <v>81</v>
+        <v>97</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>82</v>
+        <v>98</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="12" t="s">
-        <v>83</v>
+        <v>99</v>
       </c>
       <c r="B9" s="13" t="s">
-        <v>84</v>
+        <v>100</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="10" t="s">
-        <v>85</v>
+        <v>101</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>86</v>
+        <v>102</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="12" t="s">
-        <v>87</v>
+        <v>103</v>
       </c>
       <c r="B11" s="13" t="s">
-        <v>88</v>
+        <v>104</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="10" t="s">
-        <v>89</v>
+        <v>105</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>90</v>
+        <v>106</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="12" t="s">
-        <v>91</v>
+        <v>107</v>
       </c>
       <c r="B13" s="13" t="s">
-        <v>92</v>
+        <v>108</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="10" t="s">
-        <v>93</v>
+        <v>109</v>
       </c>
       <c r="B14" s="11" t="s">
-        <v>94</v>
+        <v>110</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1761,7 +2075,7 @@
     </row>
     <row r="18" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="7" t="s">
-        <v>95</v>
+        <v>111</v>
       </c>
       <c r="B18" s="7"/>
       <c r="C18" s="7"/>
@@ -1773,120 +2087,202 @@
         <v/>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="7" t="s">
-        <v>96</v>
-      </c>
-      <c r="B19" s="7"/>
-      <c r="C19" s="7"/>
-      <c r="D19" s="7"/>
-      <c r="E19" s="7"/>
-      <c r="F19" s="15"/>
-      <c r="G19" s="16" t="str">
-        <f aca="false">IF(F19="","",IF(ABS(F19-(9))&lt;=0.000000001,"Riktig","Prøv igjen"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="7" t="s">
-        <v>97</v>
-      </c>
-      <c r="B20" s="7"/>
-      <c r="C20" s="7"/>
-      <c r="D20" s="7"/>
-      <c r="E20" s="7"/>
-      <c r="F20" s="17"/>
-      <c r="G20" s="16" t="str">
-        <f aca="false">IF(F20="","",IF(UPPER(TRIM(F20))="B","Riktig","Prøv igjen"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="19" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="17" t="s">
+        <v>45</v>
+      </c>
+      <c r="B19" s="18" t="s">
+        <v>112</v>
+      </c>
+      <c r="C19" s="18"/>
+      <c r="D19" s="18"/>
+      <c r="E19" s="18"/>
+      <c r="F19" s="18"/>
+      <c r="G19" s="18"/>
+    </row>
+    <row r="21" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="7" t="s">
-        <v>98</v>
+        <v>113</v>
       </c>
       <c r="B21" s="7"/>
       <c r="C21" s="7"/>
       <c r="D21" s="7"/>
       <c r="E21" s="7"/>
-      <c r="F21" s="17"/>
+      <c r="F21" s="15"/>
       <c r="G21" s="16" t="str">
-        <f aca="false">IF(F21="","",IF(UPPER(TRIM(F21))="B","Riktig","Prøv igjen"))</f>
+        <f aca="false">IF(F21="","",IF(ABS(F21-(9))&lt;=0.000000001,"Riktig","Prøv igjen"))</f>
         <v/>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="7" t="s">
-        <v>99</v>
-      </c>
-      <c r="B22" s="7"/>
-      <c r="C22" s="7"/>
-      <c r="D22" s="7"/>
-      <c r="E22" s="7"/>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="18"/>
-      <c r="B23" s="18"/>
-      <c r="C23" s="18"/>
-      <c r="D23" s="18"/>
-      <c r="E23" s="18"/>
-      <c r="F23" s="18"/>
-      <c r="G23" s="18"/>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="18"/>
-      <c r="B24" s="18"/>
-      <c r="C24" s="18"/>
-      <c r="D24" s="18"/>
-      <c r="E24" s="18"/>
-      <c r="F24" s="18"/>
-      <c r="G24" s="18"/>
-    </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="18"/>
-      <c r="B25" s="18"/>
-      <c r="C25" s="18"/>
-      <c r="D25" s="18"/>
-      <c r="E25" s="18"/>
-      <c r="F25" s="18"/>
-      <c r="G25" s="18"/>
-    </row>
-    <row r="27" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="B27" s="6"/>
-      <c r="C27" s="6"/>
-      <c r="D27" s="6"/>
-      <c r="E27" s="6"/>
-      <c r="F27" s="6"/>
-      <c r="G27" s="6"/>
-    </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="B28" s="6"/>
-      <c r="C28" s="6"/>
-      <c r="D28" s="6"/>
-      <c r="E28" s="6"/>
-      <c r="F28" s="6"/>
-      <c r="G28" s="6"/>
+    <row r="22" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="17" t="s">
+        <v>45</v>
+      </c>
+      <c r="B22" s="18" t="s">
+        <v>114</v>
+      </c>
+      <c r="C22" s="18"/>
+      <c r="D22" s="18"/>
+      <c r="E22" s="18"/>
+      <c r="F22" s="18"/>
+      <c r="G22" s="18"/>
+    </row>
+    <row r="24" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="7" t="s">
+        <v>115</v>
+      </c>
+      <c r="B24" s="7"/>
+      <c r="C24" s="7"/>
+      <c r="D24" s="7"/>
+      <c r="E24" s="7"/>
+      <c r="F24" s="19"/>
+      <c r="G24" s="16" t="str">
+        <f aca="false">IF(F24="","",IF(UPPER(TRIM(F24))="B","Riktig","Prøv igjen"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="7" t="s">
+        <v>116</v>
+      </c>
+      <c r="B25" s="7"/>
+      <c r="C25" s="7"/>
+      <c r="D25" s="7"/>
+      <c r="E25" s="7"/>
+      <c r="F25" s="19"/>
+      <c r="G25" s="16" t="str">
+        <f aca="false">IF(F25="","",IF(UPPER(TRIM(F25))="B","Riktig","Prøv igjen"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="B26" s="7"/>
+      <c r="C26" s="7"/>
+      <c r="D26" s="7"/>
+      <c r="E26" s="7"/>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="20"/>
+      <c r="B27" s="20"/>
+      <c r="C27" s="20"/>
+      <c r="D27" s="20"/>
+      <c r="E27" s="20"/>
+      <c r="F27" s="20"/>
+      <c r="G27" s="20"/>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="20"/>
+      <c r="B28" s="20"/>
+      <c r="C28" s="20"/>
+      <c r="D28" s="20"/>
+      <c r="E28" s="20"/>
+      <c r="F28" s="20"/>
+      <c r="G28" s="20"/>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="20"/>
+      <c r="B29" s="20"/>
+      <c r="C29" s="20"/>
+      <c r="D29" s="20"/>
+      <c r="E29" s="20"/>
+      <c r="F29" s="20"/>
+      <c r="G29" s="20"/>
+    </row>
+    <row r="30" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="17" t="s">
+        <v>45</v>
+      </c>
+      <c r="B30" s="18" t="s">
+        <v>118</v>
+      </c>
+      <c r="C30" s="18"/>
+      <c r="D30" s="18"/>
+      <c r="E30" s="18"/>
+      <c r="F30" s="18"/>
+      <c r="G30" s="18"/>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="21" t="s">
+        <v>54</v>
+      </c>
+      <c r="B33" s="21"/>
+      <c r="C33" s="21"/>
+      <c r="D33" s="21"/>
+      <c r="E33" s="21"/>
+      <c r="F33" s="21"/>
+      <c r="G33" s="21"/>
+    </row>
+    <row r="34" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="22" t="s">
+        <v>119</v>
+      </c>
+      <c r="B34" s="23" t="s">
+        <v>120</v>
+      </c>
+      <c r="C34" s="23"/>
+      <c r="D34" s="23"/>
+      <c r="E34" s="23"/>
+      <c r="F34" s="23"/>
+      <c r="G34" s="23"/>
+    </row>
+    <row r="35" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A35" s="22" t="s">
+        <v>121</v>
+      </c>
+      <c r="B35" s="23" t="s">
+        <v>122</v>
+      </c>
+      <c r="C35" s="23"/>
+      <c r="D35" s="23"/>
+      <c r="E35" s="23"/>
+      <c r="F35" s="23"/>
+      <c r="G35" s="23"/>
+    </row>
+    <row r="37" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A37" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="B37" s="6"/>
+      <c r="C37" s="6"/>
+      <c r="D37" s="6"/>
+      <c r="E37" s="6"/>
+      <c r="F37" s="6"/>
+      <c r="G37" s="6"/>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A38" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="B38" s="6"/>
+      <c r="C38" s="6"/>
+      <c r="D38" s="6"/>
+      <c r="E38" s="6"/>
+      <c r="F38" s="6"/>
+      <c r="G38" s="6"/>
     </row>
   </sheetData>
-  <mergeCells count="12">
+  <mergeCells count="18">
     <mergeCell ref="A4:G4"/>
     <mergeCell ref="A5:G5"/>
     <mergeCell ref="A15:G15"/>
     <mergeCell ref="A17:E17"/>
     <mergeCell ref="A18:E18"/>
-    <mergeCell ref="A19:E19"/>
-    <mergeCell ref="A20:E20"/>
+    <mergeCell ref="B19:G19"/>
     <mergeCell ref="A21:E21"/>
-    <mergeCell ref="A22:E22"/>
-    <mergeCell ref="A23:G25"/>
-    <mergeCell ref="A27:G27"/>
-    <mergeCell ref="A28:G28"/>
+    <mergeCell ref="B22:G22"/>
+    <mergeCell ref="A24:E24"/>
+    <mergeCell ref="A25:E25"/>
+    <mergeCell ref="A26:E26"/>
+    <mergeCell ref="A27:G29"/>
+    <mergeCell ref="B30:G30"/>
+    <mergeCell ref="A33:G33"/>
+    <mergeCell ref="B34:G34"/>
+    <mergeCell ref="B35:G35"/>
+    <mergeCell ref="A37:G37"/>
+    <mergeCell ref="A38:G38"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -1903,7 +2299,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:G26"/>
+  <dimension ref="A1:G36"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="34"/>
@@ -1914,7 +2310,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>101</v>
+        <v>124</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1924,7 +2320,7 @@
     </row>
     <row r="4" customFormat="false" ht="78.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>102</v>
+        <v>125</v>
       </c>
       <c r="B4" s="6"/>
       <c r="C4" s="6"/>
@@ -1935,7 +2331,7 @@
     </row>
     <row r="5" customFormat="false" ht="108.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="7" t="s">
-        <v>103</v>
+        <v>126</v>
       </c>
       <c r="B5" s="7"/>
       <c r="C5" s="7"/>
@@ -1958,11 +2354,11 @@
       <c r="G7" s="14"/>
     </row>
     <row r="8" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="19" t="s">
-        <v>104</v>
+      <c r="A8" s="24" t="s">
+        <v>127</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>105</v>
+        <v>128</v>
       </c>
       <c r="C8" s="7"/>
       <c r="D8" s="7"/>
@@ -1971,11 +2367,11 @@
       <c r="G8" s="7"/>
     </row>
     <row r="9" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="19" t="s">
-        <v>106</v>
+      <c r="A9" s="24" t="s">
+        <v>129</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>107</v>
+        <v>130</v>
       </c>
       <c r="C9" s="7"/>
       <c r="D9" s="7"/>
@@ -1984,11 +2380,11 @@
       <c r="G9" s="7"/>
     </row>
     <row r="10" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="19" t="s">
-        <v>108</v>
+      <c r="A10" s="24" t="s">
+        <v>131</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>109</v>
+        <v>132</v>
       </c>
       <c r="C10" s="7"/>
       <c r="D10" s="7"/>
@@ -1997,11 +2393,11 @@
       <c r="G10" s="7"/>
     </row>
     <row r="11" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="19" t="s">
-        <v>110</v>
+      <c r="A11" s="24" t="s">
+        <v>133</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>111</v>
+        <v>134</v>
       </c>
       <c r="C11" s="7"/>
       <c r="D11" s="7"/>
@@ -2010,11 +2406,11 @@
       <c r="G11" s="7"/>
     </row>
     <row r="12" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="19" t="s">
-        <v>112</v>
+      <c r="A12" s="24" t="s">
+        <v>135</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>113</v>
+        <v>136</v>
       </c>
       <c r="C12" s="7"/>
       <c r="D12" s="7"/>
@@ -2023,11 +2419,11 @@
       <c r="G12" s="7"/>
     </row>
     <row r="13" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="19" t="s">
-        <v>114</v>
+      <c r="A13" s="24" t="s">
+        <v>137</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>115</v>
+        <v>138</v>
       </c>
       <c r="C13" s="7"/>
       <c r="D13" s="7"/>
@@ -2052,7 +2448,7 @@
     </row>
     <row r="16" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="7" t="s">
-        <v>116</v>
+        <v>139</v>
       </c>
       <c r="B16" s="7"/>
       <c r="C16" s="7"/>
@@ -2064,108 +2460,184 @@
         <v/>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="7" t="s">
-        <v>117</v>
-      </c>
-      <c r="B17" s="7"/>
-      <c r="C17" s="7"/>
-      <c r="D17" s="7"/>
-      <c r="E17" s="7"/>
-      <c r="F17" s="15"/>
-      <c r="G17" s="16" t="str">
-        <f aca="false">IF(F17="","",IF(ABS(F17-(2))&lt;=0.000000001,"Riktig","Prøv igjen"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="7" t="s">
-        <v>118</v>
-      </c>
-      <c r="B18" s="7"/>
-      <c r="C18" s="7"/>
-      <c r="D18" s="7"/>
-      <c r="E18" s="7"/>
-      <c r="F18" s="17"/>
-      <c r="G18" s="16" t="str">
-        <f aca="false">IF(F18="","",IF(UPPER(TRIM(F18))="C","Riktig","Prøv igjen"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="17" t="s">
+        <v>45</v>
+      </c>
+      <c r="B17" s="18" t="s">
+        <v>140</v>
+      </c>
+      <c r="C17" s="18"/>
+      <c r="D17" s="18"/>
+      <c r="E17" s="18"/>
+      <c r="F17" s="18"/>
+      <c r="G17" s="18"/>
+    </row>
+    <row r="19" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="7" t="s">
-        <v>119</v>
+        <v>141</v>
       </c>
       <c r="B19" s="7"/>
       <c r="C19" s="7"/>
       <c r="D19" s="7"/>
       <c r="E19" s="7"/>
-      <c r="F19" s="17"/>
+      <c r="F19" s="15"/>
       <c r="G19" s="16" t="str">
-        <f aca="false">IF(F19="","",IF(UPPER(TRIM(F19))="B","Riktig","Prøv igjen"))</f>
+        <f aca="false">IF(F19="","",IF(ABS(F19-(2))&lt;=0.000000001,"Riktig","Prøv igjen"))</f>
         <v/>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="7" t="s">
-        <v>120</v>
-      </c>
-      <c r="B20" s="7"/>
-      <c r="C20" s="7"/>
-      <c r="D20" s="7"/>
-      <c r="E20" s="7"/>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="18"/>
-      <c r="B21" s="18"/>
-      <c r="C21" s="18"/>
-      <c r="D21" s="18"/>
-      <c r="E21" s="18"/>
-      <c r="F21" s="18"/>
-      <c r="G21" s="18"/>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="18"/>
-      <c r="B22" s="18"/>
-      <c r="C22" s="18"/>
-      <c r="D22" s="18"/>
-      <c r="E22" s="18"/>
-      <c r="F22" s="18"/>
-      <c r="G22" s="18"/>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="18"/>
-      <c r="B23" s="18"/>
-      <c r="C23" s="18"/>
-      <c r="D23" s="18"/>
-      <c r="E23" s="18"/>
-      <c r="F23" s="18"/>
-      <c r="G23" s="18"/>
-    </row>
-    <row r="25" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="6" t="s">
-        <v>121</v>
-      </c>
-      <c r="B25" s="6"/>
-      <c r="C25" s="6"/>
-      <c r="D25" s="6"/>
-      <c r="E25" s="6"/>
-      <c r="F25" s="6"/>
-      <c r="G25" s="6"/>
-    </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="B26" s="6"/>
-      <c r="C26" s="6"/>
-      <c r="D26" s="6"/>
-      <c r="E26" s="6"/>
-      <c r="F26" s="6"/>
-      <c r="G26" s="6"/>
+    <row r="20" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="17" t="s">
+        <v>45</v>
+      </c>
+      <c r="B20" s="18" t="s">
+        <v>142</v>
+      </c>
+      <c r="C20" s="18"/>
+      <c r="D20" s="18"/>
+      <c r="E20" s="18"/>
+      <c r="F20" s="18"/>
+      <c r="G20" s="18"/>
+    </row>
+    <row r="22" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="7" t="s">
+        <v>143</v>
+      </c>
+      <c r="B22" s="7"/>
+      <c r="C22" s="7"/>
+      <c r="D22" s="7"/>
+      <c r="E22" s="7"/>
+      <c r="F22" s="19"/>
+      <c r="G22" s="16" t="str">
+        <f aca="false">IF(F22="","",IF(UPPER(TRIM(F22))="C","Riktig","Prøv igjen"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="B23" s="7"/>
+      <c r="C23" s="7"/>
+      <c r="D23" s="7"/>
+      <c r="E23" s="7"/>
+      <c r="F23" s="19"/>
+      <c r="G23" s="16" t="str">
+        <f aca="false">IF(F23="","",IF(UPPER(TRIM(F23))="B","Riktig","Prøv igjen"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="B24" s="7"/>
+      <c r="C24" s="7"/>
+      <c r="D24" s="7"/>
+      <c r="E24" s="7"/>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="20"/>
+      <c r="B25" s="20"/>
+      <c r="C25" s="20"/>
+      <c r="D25" s="20"/>
+      <c r="E25" s="20"/>
+      <c r="F25" s="20"/>
+      <c r="G25" s="20"/>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="20"/>
+      <c r="B26" s="20"/>
+      <c r="C26" s="20"/>
+      <c r="D26" s="20"/>
+      <c r="E26" s="20"/>
+      <c r="F26" s="20"/>
+      <c r="G26" s="20"/>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="20"/>
+      <c r="B27" s="20"/>
+      <c r="C27" s="20"/>
+      <c r="D27" s="20"/>
+      <c r="E27" s="20"/>
+      <c r="F27" s="20"/>
+      <c r="G27" s="20"/>
+    </row>
+    <row r="28" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="17" t="s">
+        <v>45</v>
+      </c>
+      <c r="B28" s="18" t="s">
+        <v>146</v>
+      </c>
+      <c r="C28" s="18"/>
+      <c r="D28" s="18"/>
+      <c r="E28" s="18"/>
+      <c r="F28" s="18"/>
+      <c r="G28" s="18"/>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="21" t="s">
+        <v>54</v>
+      </c>
+      <c r="B31" s="21"/>
+      <c r="C31" s="21"/>
+      <c r="D31" s="21"/>
+      <c r="E31" s="21"/>
+      <c r="F31" s="21"/>
+      <c r="G31" s="21"/>
+    </row>
+    <row r="32" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="22" t="s">
+        <v>147</v>
+      </c>
+      <c r="B32" s="23" t="s">
+        <v>148</v>
+      </c>
+      <c r="C32" s="23"/>
+      <c r="D32" s="23"/>
+      <c r="E32" s="23"/>
+      <c r="F32" s="23"/>
+      <c r="G32" s="23"/>
+    </row>
+    <row r="33" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="22" t="s">
+        <v>149</v>
+      </c>
+      <c r="B33" s="23" t="s">
+        <v>150</v>
+      </c>
+      <c r="C33" s="23"/>
+      <c r="D33" s="23"/>
+      <c r="E33" s="23"/>
+      <c r="F33" s="23"/>
+      <c r="G33" s="23"/>
+    </row>
+    <row r="35" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A35" s="6" t="s">
+        <v>151</v>
+      </c>
+      <c r="B35" s="6"/>
+      <c r="C35" s="6"/>
+      <c r="D35" s="6"/>
+      <c r="E35" s="6"/>
+      <c r="F35" s="6"/>
+      <c r="G35" s="6"/>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="B36" s="6"/>
+      <c r="C36" s="6"/>
+      <c r="D36" s="6"/>
+      <c r="E36" s="6"/>
+      <c r="F36" s="6"/>
+      <c r="G36" s="6"/>
     </row>
   </sheetData>
-  <mergeCells count="18">
+  <mergeCells count="24">
     <mergeCell ref="A4:G4"/>
     <mergeCell ref="A5:G5"/>
     <mergeCell ref="B7:G7"/>
@@ -2177,13 +2649,19 @@
     <mergeCell ref="B13:G13"/>
     <mergeCell ref="A15:E15"/>
     <mergeCell ref="A16:E16"/>
-    <mergeCell ref="A17:E17"/>
-    <mergeCell ref="A18:E18"/>
+    <mergeCell ref="B17:G17"/>
     <mergeCell ref="A19:E19"/>
-    <mergeCell ref="A20:E20"/>
-    <mergeCell ref="A21:G23"/>
-    <mergeCell ref="A25:G25"/>
-    <mergeCell ref="A26:G26"/>
+    <mergeCell ref="B20:G20"/>
+    <mergeCell ref="A22:E22"/>
+    <mergeCell ref="A23:E23"/>
+    <mergeCell ref="A24:E24"/>
+    <mergeCell ref="A25:G27"/>
+    <mergeCell ref="B28:G28"/>
+    <mergeCell ref="A31:G31"/>
+    <mergeCell ref="B32:G32"/>
+    <mergeCell ref="B33:G33"/>
+    <mergeCell ref="A35:G35"/>
+    <mergeCell ref="A36:G36"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>

--- a/pensum/ol14/OL14_Klasseoppgaver_v5.xlsx
+++ b/pensum/ol14/OL14_Klasseoppgaver_v5.xlsx
@@ -95,7 +95,7 @@
     <t xml:space="preserve">Kort oppsummert: Taylors vitenskapelige ledelse (14.1) finner den beste framgangsmåten (metodestudie), setter et normtall for tiden (tidsstudie) og knytter lønna til prestasjonen (akkord). Normtiden er derfor en av de viktigste tallene i kalkylen: er den feil, er prisen feil for hver jobb. Akkorden gir fart, men en spart time er bare verdt noe når den selges til en annen kunde, og arbeid som ikke har normtall, som dokumentasjon og opplæring, blir lett gjort sist.</t>
   </si>
   <si>
-    <t xml:space="preserve">Casen er lagt til 2026/2027. I kalkylen til Nordlys står det at et sikringsskapbytte i enebolig tar 14 montørtimer. Ida Haugen satte tallet og bruker det i hvert tilbud. Nordlys bytter om lag 120 skap i året, og timeprisen er 890 kr uten mva. Prosjekt og nybygg jobber på akkord, og akkordlagene gjør ofte skapet på 11 timer. Service har fastlønn og gjør mest feilsøking og småjobber. Ida anslår at en halv time per skap går til samsvarserklæring, opplæring av lærlingen og rydding, arbeid som ikke har noe normtall. Et styremedlem vil innføre akkord også i service. Gå fram slik: regn hva én time feil i normtiden betyr i året, regn hva akkorden frigjør, regn hva det umålte arbeidet er verdt, og ta så stilling til forslaget.</t>
+    <t xml:space="preserve">Casen er lagt til 2026/2027. I kalkylen til Nordlys står det at et sikringsskapbytte i enebolig tar 14 montørtimer. Ida Haugen satte tallet og bruker det i hvert tilbud. Nordlys bytter om lag 120 skap i året, og timeprisen er 890 kr uten merverdiavgift. Prosjekt og nybygg jobber på akkord, og akkordlagene gjør ofte skapet på 11 timer. Service har fastlønn og gjør mest feilsøking og småjobber. Ida anslår at en halv time per skap går til samsvarserklæring, opplæring av lærlingen og rydding, arbeid som ikke har noe normtall. Et styremedlem vil innføre akkord også i service. Gå fram slik: regn hva én time feil i normtiden betyr i året, regn hva akkorden frigjør, regn hva det umålte arbeidet er verdt, og ta så stilling til forslaget.</t>
   </si>
   <si>
     <t xml:space="preserve">Forutsetning</t>
@@ -116,7 +116,7 @@
     <t xml:space="preserve">120</t>
   </si>
   <si>
-    <t xml:space="preserve">Timepris uten mva</t>
+    <t xml:space="preserve">Timepris uten merverdiavgift</t>
   </si>
   <si>
     <t xml:space="preserve">890 kr</t>
@@ -299,7 +299,7 @@
     <t xml:space="preserve">Fakturerbare timer delt på betalte timer for montørene: 2 × 1 400 delt på 2 × 1 800. Tallet sier hvor godt Fjell gjør tingene riktig, ikke om det er de riktige tingene.</t>
   </si>
   <si>
-    <t xml:space="preserve">Kilde: Hjertnes, F.: Markedsføring, organisasjon og ledelse for LØM-emnet, kap. 14.2 (enhetlig ledelse), 14.3 (byråkratiteorien) og avsnittet om indre og ytre effektivitet. FEL § 12 og internkontrollforskriften § 5 (Lovdata). Fjell Elektro AS er en konstruert casebedrift.</t>
+    <t xml:space="preserve">Kilde: Hjertnes, F.: Markedsføring, organisasjon og ledelse for LØM-emnet, kap. 14.2 (enhetlig ledelse), 14.3 (byråkratiteorien) og avsnittet om indre og ytre effektivitet. Forskrift om elektriske lavspenningsanlegg (FEL) § 12 og internkontrollforskriften § 5 (Lovdata). Fjell Elektro AS er en konstruert casebedrift.</t>
   </si>
   <si>
     <t xml:space="preserve">B1 · Nordlys: hvem skal lede solcelle og lading?</t>

--- a/pensum/ol14/OL14_Klasseoppgaver_v5.xlsx
+++ b/pensum/ol14/OL14_Klasseoppgaver_v5.xlsx
@@ -26,7 +26,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="152">
   <si>
-    <t xml:space="preserve">Klasseoppgaver til Organisasjon og ledelse kapittel 14: Klassiske organisasjonsteorier (V5)</t>
+    <t xml:space="preserve">Klasseoppgaver til Organisasjon og ledelse kapittel 14: Klassiske organisasjonsteorier (versjon 5)</t>
   </si>
   <si>
     <t xml:space="preserve">LØM · Fagskolen Oslo, Avdeling Elkraft · versjon 5, oktober 2026</t>
